--- a/artfynd/A 7669-2025 artfynd.xlsx
+++ b/artfynd/A 7669-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124296496</v>
+        <v>125844136</v>
       </c>
       <c r="B2" t="n">
-        <v>78546</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lokarna, Lokarna, Jmt</t>
+          <t>Sönnertjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>527069</v>
+        <v>527248</v>
       </c>
       <c r="R2" t="n">
-        <v>6965123</v>
+        <v>6965096</v>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>13:54</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>13:54</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,65 +760,60 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124295207</v>
+        <v>125844198</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lokarna, Lokarna, Jmt</t>
+          <t>Sönnertjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>527141</v>
+        <v>527275</v>
       </c>
       <c r="R3" t="n">
-        <v>6965186</v>
+        <v>6965141</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>13:35</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>13:35</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,56 +853,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124296417</v>
+        <v>125844194</v>
       </c>
       <c r="B4" t="n">
-        <v>78547</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -940,37 +880,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lokarna, Lokarna, Jmt</t>
+          <t>Sönnertjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>527077</v>
+        <v>527275</v>
       </c>
       <c r="R4" t="n">
-        <v>6965121</v>
+        <v>6965073</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -994,22 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>13:46</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>13:46</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,12 +954,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1039,12 +969,7 @@
         <v>124295846</v>
       </c>
       <c r="B5" t="n">
-        <v>79892</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1178,69 +1103,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124294897</v>
+        <v>125844150</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lokarna, Lokarna, Jmt</t>
+          <t>Sönnertjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527167</v>
+        <v>527214</v>
       </c>
       <c r="R6" t="n">
-        <v>6965201</v>
+        <v>6965117</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1264,27 +1168,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:27</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:27</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Minst 60 plantor och 4 vinterståndare inom ca 2 x 0,5 m2 yta.</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1293,34 +1182,28 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125844168</v>
+        <v>125844151</v>
       </c>
       <c r="B7" t="n">
-        <v>80083</v>
+        <v>80433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1352,7 +1235,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>527272</v>
+        <v>527273</v>
       </c>
       <c r="R7" t="n">
         <v>6965136</v>
@@ -1414,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125844167</v>
+        <v>125844195</v>
       </c>
       <c r="B8" t="n">
-        <v>80083</v>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,21 +1308,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1449,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>527273</v>
+        <v>527323</v>
       </c>
       <c r="R8" t="n">
-        <v>6965136</v>
+        <v>6965169</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1511,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125844151</v>
+        <v>125844196</v>
       </c>
       <c r="B9" t="n">
-        <v>80084</v>
+        <v>93197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1522,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1546,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>527273</v>
+        <v>527301</v>
       </c>
       <c r="R9" t="n">
-        <v>6965136</v>
+        <v>6965140</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1608,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125844189</v>
+        <v>125844197</v>
       </c>
       <c r="B10" t="n">
-        <v>78980</v>
+        <v>93197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1619,21 +1502,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1643,10 +1526,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>527307</v>
+        <v>527273</v>
       </c>
       <c r="R10" t="n">
-        <v>6965182</v>
+        <v>6965073</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1679,11 +1562,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-06-09</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1710,48 +1588,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125844145</v>
+        <v>124295207</v>
       </c>
       <c r="B11" t="n">
-        <v>98382</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sönnertjärnen, Jmt</t>
+          <t>Lokarna, Lokarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>527278</v>
+        <v>527141</v>
       </c>
       <c r="R11" t="n">
-        <v>6965138</v>
+        <v>6965186</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1775,12 +1653,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1791,48 +1679,73 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125844195</v>
+        <v>125844189</v>
       </c>
       <c r="B12" t="n">
-        <v>92535</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1842,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>527323</v>
+        <v>527307</v>
       </c>
       <c r="R12" t="n">
-        <v>6965169</v>
+        <v>6965182</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1878,6 +1791,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1904,32 +1822,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125844177</v>
+        <v>125844191</v>
       </c>
       <c r="B13" t="n">
-        <v>98694</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219880</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1939,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>527066</v>
+        <v>527081</v>
       </c>
       <c r="R13" t="n">
-        <v>6965195</v>
+        <v>6965161</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2001,32 +1919,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125844196</v>
+        <v>125844192</v>
       </c>
       <c r="B14" t="n">
-        <v>92535</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2036,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>527301</v>
+        <v>527214</v>
       </c>
       <c r="R14" t="n">
-        <v>6965140</v>
+        <v>6965117</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2101,11 +2019,11 @@
         <v>125844193</v>
       </c>
       <c r="B15" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2195,32 +2113,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125844137</v>
+        <v>125844155</v>
       </c>
       <c r="B16" t="n">
-        <v>79598</v>
+        <v>79351</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2230,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>527301</v>
+        <v>527333</v>
       </c>
       <c r="R16" t="n">
-        <v>6965140</v>
+        <v>6965188</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2292,32 +2210,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125844144</v>
+        <v>125844135</v>
       </c>
       <c r="B17" t="n">
-        <v>98382</v>
+        <v>83307</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221952</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2327,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>527307</v>
+        <v>527322</v>
       </c>
       <c r="R17" t="n">
-        <v>6965182</v>
+        <v>6965188</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2389,32 +2307,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125844191</v>
+        <v>125844147</v>
       </c>
       <c r="B18" t="n">
-        <v>78980</v>
+        <v>78685</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6443</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sm.) A.Massal.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2424,10 +2342,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>527081</v>
+        <v>527268</v>
       </c>
       <c r="R18" t="n">
-        <v>6965161</v>
+        <v>6965088</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2486,10 +2404,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125844135</v>
+        <v>124296496</v>
       </c>
       <c r="B19" t="n">
-        <v>75075</v>
+        <v>79084</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2497,37 +2415,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sönnertjärnen, Jmt</t>
+          <t>Lokarna, Lokarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>527322</v>
+        <v>527069</v>
       </c>
       <c r="R19" t="n">
-        <v>6965188</v>
+        <v>6965123</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2551,12 +2469,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2571,44 +2499,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125844198</v>
+        <v>125844137</v>
       </c>
       <c r="B20" t="n">
-        <v>91819</v>
+        <v>79946</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>760</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2618,10 +2546,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>527275</v>
+        <v>527301</v>
       </c>
       <c r="R20" t="n">
-        <v>6965141</v>
+        <v>6965140</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2677,6 +2605,1508 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>125844165</v>
+      </c>
+      <c r="B21" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Sönnertjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>527214</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6965117</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>125844167</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Sönnertjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>527273</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6965136</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>125844168</v>
+      </c>
+      <c r="B23" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Sönnertjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>527272</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6965136</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>125844169</v>
+      </c>
+      <c r="B24" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Sönnertjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>527249</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6965099</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>125844170</v>
+      </c>
+      <c r="B25" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Sönnertjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>527235</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6965074</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>125844172</v>
+      </c>
+      <c r="B26" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Sönnertjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>527247</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6965119</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>125844140</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Sönnertjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>527214</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6965117</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>125844176</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99456</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>219880</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Kransrams</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Polygonatum verticillatum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Sönnertjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>527066</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6965195</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>124294897</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Lokarna, Lokarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>527167</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6965201</v>
+      </c>
+      <c r="S29" t="n">
+        <v>9</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Minst 60 plantor och 4 vinterståndare inom ca 2 x 0,5 m2 yta.</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>125844183</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Sönnertjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>527247</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6965099</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>125844184</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Sönnertjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>527222</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6965071</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>125844144</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Sönnertjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>527307</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6965182</v>
+      </c>
+      <c r="S32" t="n">
+        <v>25</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>125844145</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Sönnertjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>527278</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6965138</v>
+      </c>
+      <c r="S33" t="n">
+        <v>25</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>125844146</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Sönnertjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>527247</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6965119</v>
+      </c>
+      <c r="S34" t="n">
+        <v>25</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>124296417</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Lokarna, Lokarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>527077</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6965121</v>
+      </c>
+      <c r="S35" t="n">
+        <v>9</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7669-2025 artfynd.xlsx
+++ b/artfynd/A 7669-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AZ35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125844136</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125844198</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125844194</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124295846</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125844150</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1294,6 +1324,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125844151</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1391,6 +1426,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125844195</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1488,6 +1528,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125844196</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1585,6 +1630,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125844197</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1717,6 +1767,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124295207</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1819,6 +1874,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125844189</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1916,6 +1976,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125844191</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2013,6 +2078,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125844192</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2110,6 +2180,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125844193</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2207,6 +2282,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125844155</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2304,6 +2384,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125844135</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2401,6 +2486,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125844147</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2508,6 +2598,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124296496</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2605,6 +2700,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125844137</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2702,6 +2802,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125844165</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2799,6 +2904,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125844167</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2896,6 +3006,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125844168</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2993,6 +3108,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125844169</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3090,6 +3210,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125844170</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3187,6 +3312,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125844172</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3284,6 +3414,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125844140</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3381,6 +3516,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125844176</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3515,6 +3655,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124294897</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3612,6 +3757,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125844183</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3709,6 +3859,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125844184</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3806,6 +3961,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125844144</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3903,6 +4063,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125844145</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4000,6 +4165,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125844146</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4107,8 +4277,49 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124296417</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>